--- a/data/mu_slow_estimates_from_literature.xlsx
+++ b/data/mu_slow_estimates_from_literature.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lh667\PersonalGitHub\MINA_TB\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{73088D97-D635-42D3-97E9-B588DAA93F04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAE55D23-F4C7-4521-9B04-A9467CF43A37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{F6F9CD2D-37BC-4380-B528-15923D33CB62}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F6F9CD2D-37BC-4380-B528-15923D33CB62}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="18">
   <si>
     <t>study</t>
   </si>
@@ -69,6 +69,27 @@
   </si>
   <si>
     <t>Barnett-1971</t>
+  </si>
+  <si>
+    <t>?</t>
+  </si>
+  <si>
+    <t>model</t>
+  </si>
+  <si>
+    <t>TST survey</t>
+  </si>
+  <si>
+    <t>review of trials</t>
+  </si>
+  <si>
+    <t>statistical model</t>
+  </si>
+  <si>
+    <t>model structure E?</t>
+  </si>
+  <si>
+    <t>survey</t>
   </si>
 </sst>
 </file>
@@ -446,148 +467,190 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32A150FF-1861-4631-9BB9-3D313DD0D2F4}">
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="17" customWidth="1"/>
     <col min="2" max="2" width="10.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B1">
-        <v>8.9999999999999999E-8</v>
-      </c>
-      <c r="C1">
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="D1">
-        <v>2.9899999999999999E-2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2">
+        <v>5.2700000000000004E-3</v>
+      </c>
+      <c r="E2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3">
+        <v>2.5600000000000002E-3</v>
+      </c>
+      <c r="E3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4">
+        <v>1E-3</v>
+      </c>
+      <c r="E4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
         <v>5</v>
       </c>
-      <c r="B2">
-        <v>1E-4</v>
-      </c>
-      <c r="C2">
-        <v>1.0000000000000001E-5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3">
-        <v>1E-4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4">
-        <v>2.3000000000000001E-4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
       <c r="B5">
-        <v>4.0000000000000002E-4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+        <v>8.9999999999999998E-4</v>
+      </c>
+      <c r="C5">
+        <v>5.5999999999999995E-4</v>
+      </c>
+      <c r="E5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B6">
-        <v>5.8E-4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+        <v>8.4800000000000001E-4</v>
+      </c>
+      <c r="E6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B7">
-        <v>5.9400000000000002E-4</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+        <v>8.4000000000000003E-4</v>
+      </c>
+      <c r="E7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>4</v>
       </c>
       <c r="B8">
         <v>7.2000000000000005E-4</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B9">
-        <v>8.4000000000000003E-4</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+        <v>5.9400000000000002E-4</v>
+      </c>
+      <c r="E9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10">
+        <v>5.8E-4</v>
+      </c>
+      <c r="E10" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11">
+        <v>4.0000000000000002E-4</v>
+      </c>
+      <c r="E11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>8</v>
+      </c>
+      <c r="B12">
+        <v>2.3000000000000001E-4</v>
+      </c>
+      <c r="E12" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
         <v>5</v>
       </c>
-      <c r="B10">
-        <v>8.4800000000000001E-4</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>5</v>
-      </c>
-      <c r="B11">
-        <v>8.9999999999999998E-4</v>
-      </c>
-      <c r="C11">
-        <v>5.5999999999999995E-4</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>9</v>
-      </c>
-      <c r="B12">
-        <v>1E-3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>6</v>
-      </c>
       <c r="B13">
-        <v>2.5600000000000002E-3</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+        <v>1E-4</v>
+      </c>
+      <c r="C13">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="E13" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B14">
-        <v>5.2700000000000004E-3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+        <v>1E-4</v>
+      </c>
+      <c r="E14" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>0</v>
-      </c>
-      <c r="B15" t="s">
-        <v>1</v>
+        <v>7</v>
+      </c>
+      <c r="B15">
+        <v>8.9999999999999999E-8</v>
+      </c>
+      <c r="C15">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="D15">
+        <v>2.9899999999999999E-2</v>
+      </c>
+      <c r="E15" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A1:D15">
-    <sortCondition ref="B1:B15"/>
+    <sortCondition descending="1" ref="B14:B15"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
